--- a/template.xlsx
+++ b/template.xlsx
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AR21" s="30" t="inlineStr">
         <is>
-          <t>093-482-4623</t>
+          <t>093-482-4622</t>
         </is>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AR19" s="30" t="inlineStr">
         <is>
-          <t>090-2850-8650</t>
+          <t>093-482-4622</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AR21" s="30" t="inlineStr">
         <is>
-          <t>093-482-4622</t>
+          <t>093-482-4623</t>
         </is>
       </c>
     </row>
